--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484721_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484721_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3404</v>
+        <v>6.8115</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3975</v>
+        <v>6.7099</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0571</v>
+        <v>0.1016</v>
       </c>
       <c r="G2" t="n">
         <v>5.9451</v>
@@ -610,13 +610,13 @@
         <v>1.6983</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6613</v>
+        <v>-0.1901</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9871</v>
+        <v>-0.6746</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3257</v>
+        <v>0.4845</v>
       </c>
       <c r="V2" t="n">
         <v>0.3018</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3403</v>
+        <v>5.9774</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4506</v>
+        <v>5.1141</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8897</v>
+        <v>0.8633</v>
       </c>
       <c r="G3" t="n">
         <v>3.9935</v>
@@ -688,13 +688,13 @@
         <v>1.6983</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1628</v>
+        <v>0.4743</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6931</v>
+        <v>-0.0296</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5303</v>
+        <v>0.5039</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. MARCO CLIMENT</t>
+          <t>L. CERVANTES GUERRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9705</v>
+        <v>3.2287</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7122</v>
+        <v>2.2741</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2584</v>
+        <v>0.9546</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4124</v>
+        <v>1.382</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4573</v>
+        <v>0.4445</v>
       </c>
       <c r="I4" t="n">
-        <v>0.955</v>
+        <v>0.9375</v>
       </c>
       <c r="J4" t="n">
-        <v>5.445</v>
+        <v>1.4482</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8409</v>
+        <v>0.576</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6041</v>
+        <v>0.8723</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0326</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3836</v>
+        <v>-0.1315</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.649</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.774</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7659</v>
+        <v>0.0163</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1357</v>
+        <v>-0.4193</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6302</v>
+        <v>0.4356</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3208</v>
+        <v>0.3208</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9054</v>
+        <v>1.2452</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2262</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. CERVANTES GUERRA</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8285</v>
+        <v>2.07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0591</v>
+        <v>3.1614</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7694</v>
+        <v>-1.0915</v>
       </c>
       <c r="G5" t="n">
-        <v>1.382</v>
+        <v>5.9707</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4445</v>
+        <v>0.5024</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9375</v>
+        <v>5.4683</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4482</v>
+        <v>6.7523</v>
       </c>
       <c r="K5" t="n">
-        <v>0.576</v>
+        <v>1.4791</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8723</v>
+        <v>5.2732</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.7815</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1315</v>
+        <v>-0.9767</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.1951</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5096</v>
+        <v>-2.6418</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5096</v>
+        <v>1.1322</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3839</v>
+        <v>-0.0138</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6343</v>
+        <v>-0.4395</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2505</v>
+        <v>0.4257</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3208</v>
+        <v>-1.2452</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2452</v>
+        <v>0.6226</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9244</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>F. MARCO CLIMENT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1867</v>
+        <v>1.9131</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9078</v>
+        <v>2.3426</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7211</v>
+        <v>-0.4294</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9707</v>
+        <v>3.4124</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5024</v>
+        <v>2.4573</v>
       </c>
       <c r="I6" t="n">
-        <v>5.4683</v>
+        <v>0.955</v>
       </c>
       <c r="J6" t="n">
-        <v>6.7523</v>
+        <v>5.445</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4791</v>
+        <v>3.8409</v>
       </c>
       <c r="L6" t="n">
-        <v>5.2732</v>
+        <v>1.6041</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7815</v>
+        <v>-2.0326</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9767</v>
+        <v>-1.3836</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1951</v>
+        <v>-0.649</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.6418</v>
+        <v>-1.887</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.774</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1322</v>
+        <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1029</v>
+        <v>0.7085</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6931</v>
+        <v>-0.2339</v>
       </c>
       <c r="U6" t="n">
-        <v>0.796</v>
+        <v>0.9424</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2452</v>
+        <v>-0.3208</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6226</v>
+        <v>0.9054</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8678</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1475</v>
+        <v>0.174</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1475</v>
+        <v>0.174</v>
       </c>
       <c r="G7" t="n">
         <v>0.1299</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6071</v>
+        <v>-0.6819</v>
       </c>
       <c r="E8" t="n">
-        <v>1.092</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.699</v>
+        <v>-1.5403</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0437</v>
@@ -1078,13 +1078,13 @@
         <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1293</v>
+        <v>-0.2041</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0617</v>
+        <v>-0.1718</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.191</v>
+        <v>-0.0323</v>
       </c>
       <c r="V8" t="n">
         <v>0.9434</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9835</v>
+        <v>-0.7802</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5285</v>
+        <v>-1.431</v>
       </c>
       <c r="F9" t="n">
-        <v>0.545</v>
+        <v>0.6508</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0787</v>
@@ -1156,13 +1156,13 @@
         <v>0.3774</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2822</v>
+        <v>-0.0789</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3527</v>
+        <v>-0.2553</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.1764</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9163</v>
+        <v>-2.797</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2869</v>
+        <v>-1.2998</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6295</v>
+        <v>-1.4972</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1715</v>
@@ -1234,13 +1234,13 @@
         <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>1.576</v>
+        <v>0.6953</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6547</v>
+        <v>0.6418</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.0535</v>
       </c>
       <c r="V10" t="n">
         <v>-1.566</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. FONT FENOLLAR</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7835</v>
+        <v>-3.1252</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5279</v>
+        <v>-3.4968</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2556</v>
+        <v>0.3716</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3464</v>
+        <v>-1.7523</v>
       </c>
       <c r="H11" t="n">
-        <v>3.373</v>
+        <v>-1.1895</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.0266</v>
+        <v>-0.5628</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1991</v>
+        <v>-1.3993</v>
       </c>
       <c r="K11" t="n">
-        <v>4.057</v>
+        <v>-0.7497</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8579</v>
+        <v>-0.6496</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8526</v>
+        <v>-0.353</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.4398</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1687</v>
+        <v>0.0868</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.0192</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9627</v>
+        <v>-2.0757</v>
       </c>
       <c r="R11" t="n">
         <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8089</v>
+        <v>0.0611</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7642</v>
+        <v>-0.0218</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0446</v>
+        <v>0.0829</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3018</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>A. FONT FENOLLAR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8177</v>
+        <v>-3.2027</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0041</v>
+        <v>-2.0793</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1864</v>
+        <v>-1.1233</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7523</v>
+        <v>0.3464</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1895</v>
+        <v>3.373</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5628</v>
+        <v>-3.0266</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3993</v>
+        <v>2.1991</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7497</v>
+        <v>4.057</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6496</v>
+        <v>-1.8579</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.353</v>
+        <v>-1.8526</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4398</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0868</v>
+        <v>-1.1687</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1322</v>
+        <v>-3.0192</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0757</v>
+        <v>-3.9627</v>
       </c>
       <c r="R12" t="n">
         <v>0.9435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6313</v>
+        <v>-0.2281</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5291</v>
+        <v>-0.3157</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1023</v>
+        <v>0.0876</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3018</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.705800000000002</v>
+        <v>9.587700000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>11.2718</v>
+        <v>12.1536</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5659</v>
+        <v>-2.5658</v>
       </c>
       <c r="G13" t="n">
         <v>16.1338</v>
@@ -1447,13 +1447,13 @@
         <v>18.2109</v>
       </c>
       <c r="L13" t="n">
-        <v>8.2235</v>
+        <v>8.223500000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-10.3004</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.839799999999999</v>
+        <v>-6.8398</v>
       </c>
       <c r="O13" t="n">
         <v>-3.4608</v>
@@ -1468,13 +1468,13 @@
         <v>11.322</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4027000000000003</v>
+        <v>1.2846</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.8015</v>
+        <v>-1.9197</v>
       </c>
       <c r="U13" t="n">
-        <v>3.2042</v>
+        <v>3.2043</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1696</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2007</v>
+        <v>1.0228</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5148</v>
+        <v>2.7097</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3142</v>
+        <v>-1.6869</v>
       </c>
       <c r="G14" t="n">
         <v>-1.7168</v>
@@ -1546,13 +1546,13 @@
         <v>3.2079</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3704</v>
+        <v>0.1925</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8542</v>
+        <v>-0.6594</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2246</v>
+        <v>0.8519</v>
       </c>
       <c r="V14" t="n">
         <v>1.2262</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. FERRISI</t>
+          <t>S. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2701</v>
+        <v>0.4726</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0588</v>
+        <v>4.3564</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2113</v>
+        <v>-3.8838</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2113</v>
+        <v>-0.2114</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2113</v>
+        <v>-1.8501</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1.6387</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>4.8641</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1.5808</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.2834</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2113</v>
+        <v>-5.0755</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2113</v>
+        <v>-3.4309</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-1.6447</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.4531</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.3966</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0588</v>
+        <v>-0.2221</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0588</v>
+        <v>-0.8094</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.5873</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3203</v>
+        <v>-0.2409</v>
       </c>
       <c r="E16" t="n">
         <v>-0.9865</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6662</v>
+        <v>0.7456</v>
       </c>
       <c r="G16" t="n">
         <v>-1.2158</v>
@@ -1702,13 +1702,13 @@
         <v>0.3774</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1235</v>
+        <v>-0.0441</v>
       </c>
       <c r="T16" t="n">
         <v>-0.3992</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2757</v>
+        <v>0.3551</v>
       </c>
       <c r="V16" t="n">
         <v>0.6415999999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. DURAN OLMOS</t>
+          <t>M. FERRISI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3936</v>
+        <v>-0.2701</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0047</v>
+        <v>-0.0588</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3983</v>
+        <v>-0.2113</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.9893</v>
+        <v>-0.2113</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2161</v>
+        <v>-0.2113</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6601</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5071</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1672</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3292</v>
+        <v>-0.2113</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7233</v>
+        <v>-0.2113</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6059</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1992</v>
+        <v>-0.0588</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6647999999999999</v>
+        <v>-0.0588</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5344</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. GALVEZ ARROYO</t>
+          <t>I. DURAN OLMOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5245</v>
+        <v>-1.0492</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6744</v>
+        <v>-0.6773</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.1989</v>
+        <v>-0.3718</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2114</v>
+        <v>-2.9893</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8501</v>
+        <v>-1.2161</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6387</v>
+        <v>-1.7731</v>
       </c>
       <c r="J18" t="n">
-        <v>4.8641</v>
+        <v>-0.6601</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5808</v>
+        <v>0.5071</v>
       </c>
       <c r="L18" t="n">
-        <v>3.2834</v>
+        <v>-1.1672</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.0755</v>
+        <v>-2.3292</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.4309</v>
+        <v>-1.7233</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6447</v>
+        <v>-0.6059</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4531</v>
+        <v>1.6983</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.3966</v>
+        <v>1.6983</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2192</v>
+        <v>0.5436</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4915</v>
+        <v>-0.0172</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2722</v>
+        <v>0.5608</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.547</v>
+        <v>-0.3018</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7922</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4897</v>
+        <v>-1.2972</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0591</v>
+        <v>0.1357</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4306</v>
+        <v>-1.4329</v>
       </c>
       <c r="G19" t="n">
         <v>-3.6714</v>
@@ -1936,13 +1936,13 @@
         <v>3.2079</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0635</v>
+        <v>0.129</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.548</v>
+        <v>-0.3531</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4845</v>
+        <v>0.4821</v>
       </c>
       <c r="V19" t="n">
         <v>1.8678</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4296</v>
+        <v>-2.5126</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4736</v>
+        <v>0.1813</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9032</v>
+        <v>-2.6939</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0324</v>
@@ -2014,13 +2014,13 @@
         <v>2.6418</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4332</v>
+        <v>0.3502</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1016</v>
+        <v>-0.1907</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3316</v>
+        <v>0.5409</v>
       </c>
       <c r="V20" t="n">
         <v>0.3018</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4788</v>
+        <v>-4.1818</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9972</v>
+        <v>-3.0947</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4816</v>
+        <v>-1.0871</v>
       </c>
       <c r="G21" t="n">
         <v>-4.0853</v>
@@ -2092,13 +2092,13 @@
         <v>2.4531</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9406</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6191</v>
+        <v>-0.7165</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3215</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-0.019</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.7059</v>
+        <v>-8.0564</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5659</v>
+        <v>2.5658</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.2719</v>
+        <v>-10.6221</v>
       </c>
       <c r="G22" t="n">
         <v>-16.1337</v>
@@ -2140,13 +2140,13 @@
         <v>-11.3711</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.762499999999999</v>
+        <v>-4.7625</v>
       </c>
       <c r="J22" t="n">
         <v>10.3004</v>
       </c>
       <c r="K22" t="n">
-        <v>6.839799999999999</v>
+        <v>6.8398</v>
       </c>
       <c r="L22" t="n">
         <v>3.4608</v>
@@ -2158,7 +2158,7 @@
         <v>-18.211</v>
       </c>
       <c r="O22" t="n">
-        <v>-8.223299999999998</v>
+        <v>-8.2233</v>
       </c>
       <c r="P22" t="n">
         <v>5.661</v>
@@ -2170,19 +2170,19 @@
         <v>16.983</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4028</v>
+        <v>0.2467000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.204400000000001</v>
+        <v>-3.2043</v>
       </c>
       <c r="U22" t="n">
-        <v>2.8015</v>
+        <v>3.451</v>
       </c>
       <c r="V22" t="n">
         <v>2.1696</v>
       </c>
       <c r="W22" t="n">
-        <v>6.7916</v>
+        <v>6.791600000000001</v>
       </c>
       <c r="X22" t="n">
         <v>-4.622</v>
